--- a/docs/frontend_기능명세서.xlsx
+++ b/docs/frontend_기능명세서.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="429">
   <si>
     <t>ID</t>
   </si>
@@ -39,6 +39,12 @@
     <t>연동 API / Socket 이벤트</t>
   </si>
   <si>
+    <t>개발 상태</t>
+  </si>
+  <si>
+    <t>구현 메모</t>
+  </si>
+  <si>
     <t>FE-COM-01</t>
   </si>
   <si>
@@ -60,6 +66,12 @@
     <t>POST /api/v1/auth/refresh</t>
   </si>
   <si>
+    <t>완료</t>
+  </si>
+  <si>
+    <t>axios + 401 시 토큰 재발급(단일 실행) 후 재시도</t>
+  </si>
+  <si>
     <t>FE-COM-02</t>
   </si>
   <si>
@@ -72,6 +84,9 @@
     <t>GET /api/v1/users/me</t>
   </si>
   <si>
+    <t>RequireAuth</t>
+  </si>
+  <si>
     <t>FE-COM-03</t>
   </si>
   <si>
@@ -84,6 +99,9 @@
     <t>session:join, session:resume</t>
   </si>
   <si>
+    <t>백엔드 소켓 미구현 → 개발 시 목 소켓</t>
+  </si>
+  <si>
     <t>FE-COM-04</t>
   </si>
   <si>
@@ -96,6 +114,9 @@
     <t>-</t>
   </si>
   <si>
+    <t>헤더, 모달, 토스트, 로딩/오류, 반응형, 다크 모드</t>
+  </si>
+  <si>
     <t>FE-COM-05</t>
   </si>
   <si>
@@ -117,6 +138,12 @@
     <t>POST /api/v1/reports</t>
   </si>
   <si>
+    <t>미구현</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
     <t>FE-COM-06</t>
   </si>
   <si>
@@ -126,6 +153,12 @@
     <t>키보드 내비게이션, 스크린리더 라벨, 서술 영역 aria-live</t>
   </si>
   <si>
+    <t>부분</t>
+  </si>
+  <si>
+    <t>기본 aria 속성만</t>
+  </si>
+  <si>
     <t>FE-AUTH-01</t>
   </si>
   <si>
@@ -147,6 +180,9 @@
     <t>POST /api/v1/auth/signup</t>
   </si>
   <si>
+    <t>완료(목 API)</t>
+  </si>
+  <si>
     <t>FE-AUTH-02</t>
   </si>
   <si>
@@ -162,6 +198,9 @@
     <t>POST /api/v1/auth/login, GET /api/v1/auth/oauth/:provider</t>
   </si>
   <si>
+    <t>이메일 로그인만 (소셜 로그인 P1 제외), 목 API</t>
+  </si>
+  <si>
     <t>FE-AUTH-03</t>
   </si>
   <si>
@@ -264,6 +303,9 @@
     <t>GET /api/v1/scenarios/trending, GET /api/v1/scenarios?sort=rating, GET /api/v1/sessions?status=lobby</t>
   </si>
   <si>
+    <t>인기/평점 시나리오, 참여 가능한 방, 초대 코드 입력, 방 만들기</t>
+  </si>
+  <si>
     <t>FE-SCN-01</t>
   </si>
   <si>
@@ -303,6 +345,9 @@
     <t>(목록 응답 사용)</t>
   </si>
   <si>
+    <t>shared/ui/ScenarioCard (홈에서 사용)</t>
+  </si>
+  <si>
     <t>FE-SCN-03</t>
   </si>
   <si>
@@ -570,6 +615,9 @@
     <t>POST /api/v1/scenarios/:scenarioId/test-sessions, PATCH /api/v1/sessions/:sessionId/debug/state</t>
   </si>
   <si>
+    <t>1인 플레이(/play) + 주사위 고정. 플래그/스탯 편집 패널 없음</t>
+  </si>
+  <si>
     <t>FE-EDT-13</t>
   </si>
   <si>
@@ -759,6 +807,9 @@
     <t>narration:start/chunk/end</t>
   </si>
   <si>
+    <t>1인 플레이에서 스트리밍 서술 (NDJSON)</t>
+  </si>
+  <si>
     <t>FE-PLY-02</t>
   </si>
   <si>
@@ -774,6 +825,9 @@
     <t>round:start, action:submit, action:accepted, round:locked</t>
   </si>
   <si>
+    <t>자유 입력 + 행동 버튼. 라운드/제출 잠금 없음</t>
+  </si>
+  <si>
     <t>FE-PLY-03</t>
   </si>
   <si>
@@ -804,6 +858,9 @@
     <t>engine:result</t>
   </si>
   <si>
+    <t>판정 결과(굴림+보정=합계 vs 목표) 표시. 애니메이션 없음</t>
+  </si>
+  <si>
     <t>FE-PLY-05</t>
   </si>
   <si>
@@ -819,6 +876,9 @@
     <t>GET …/characters/:characterId, state:update</t>
   </si>
   <si>
+    <t>1인 캐릭터 시트 (HP, 스탯, 상태이상, 소지품)</t>
+  </si>
+  <si>
     <t>FE-PLY-06</t>
   </si>
   <si>
@@ -918,6 +978,9 @@
     <t>turn:start, turn:timeout, action:submit</t>
   </si>
   <si>
+    <t>적 HP, 공격/도주 버튼. 이니셔티브/턴 타이머 없음</t>
+  </si>
+  <si>
     <t>FE-PLY-13</t>
   </si>
   <si>
@@ -1011,6 +1074,9 @@
     <t>session:ended</t>
   </si>
   <si>
+    <t>플레이 화면 안에 엔딩 표시</t>
+  </si>
+  <si>
     <t>FE-RES-02</t>
   </si>
   <si>
@@ -1110,6 +1176,42 @@
     <t>GET /api/v1/admin/metrics/llm</t>
   </si>
   <si>
+    <t>FE-PLAY-01</t>
+  </si>
+  <si>
+    <t>1인 플레이</t>
+  </si>
+  <si>
+    <t>/play</t>
+  </si>
+  <si>
+    <t>1인 플레이 시작</t>
+  </si>
+  <si>
+    <t>시나리오·프리셋 캐릭터 선택, AI 상태 표시</t>
+  </si>
+  <si>
+    <t>GET /api/v1/play/scenarios, GET /api/v1/play/ai-status, POST /api/v1/play/games</t>
+  </si>
+  <si>
+    <t>명세 외 추가 (1인 플레이)</t>
+  </si>
+  <si>
+    <t>FE-PLAY-02</t>
+  </si>
+  <si>
+    <t>/play/:gameId</t>
+  </si>
+  <si>
+    <t>1인 플레이 화면</t>
+  </si>
+  <si>
+    <t>진행 기록, 스트리밍 서술, 자유 입력/행동 버튼, 캐릭터 시트, 전투, 주사위 고정</t>
+  </si>
+  <si>
+    <t>GET /api/v1/play/games/:gameId, POST …/actions (NDJSON), PATCH …/debug</t>
+  </si>
+  <si>
     <t>Route</t>
   </si>
   <si>
@@ -1195,6 +1297,9 @@
   </si>
   <si>
     <t>기능명세서.md의 기능 ID (F-XXX-NN). "공통"은 특정 기능에 속하지 않는 공통 인프라</t>
+  </si>
+  <si>
+    <t>완료 = 동작 확인 / 완료(목 API) = 프론트는 완료, 백엔드 미구현이라 개발용 목 API로 동작 / 부분 = 일부 구현 / 미구현 (기준일 2026-10-13)</t>
   </si>
 </sst>
 </file>
@@ -1220,7 +1325,7 @@
       <b/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1239,7 +1344,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD5F0DC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFF4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0F0F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF1CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCE8FA"/>
       </patternFill>
     </fill>
     <fill>
@@ -1275,7 +1400,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1292,10 +1417,22 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1644,7 +1781,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:J70"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1654,9 +1791,11 @@
     <col min="5" max="5" width="22" customWidth="1"/>
     <col min="6" max="6" width="62" customWidth="1"/>
     <col min="8" max="8" width="60" customWidth="1"/>
+    <col min="9" max="9" width="13" customWidth="1"/>
+    <col min="10" max="10" width="48" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="22" customHeight="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1681,1759 +1820,2231 @@
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="C3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="E3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="3" t="s">
+      <c r="H3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J3" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G6" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H6" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I7" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G10" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E8" s="3" t="s">
+      <c r="H10" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="I10" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" s="3" t="s">
+      <c r="J10" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="G12" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E9" s="3" t="s">
+      <c r="H12" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="I15" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="G22" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="I26" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="I28" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="I29" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="I30" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="I31" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="G32" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="I32" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="I33" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="I34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" s="3" t="s">
+      <c r="J34" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="G35" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="3" t="s">
+      <c r="H35" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="I35" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="G36" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="I36" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G37" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="H37" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="I37" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="I38" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C12" s="3" t="s">
+      <c r="J38" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="I39" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I40" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="I41" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="I42" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="I43" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="I44" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="I45" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="I46" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="I47" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="I48" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="I49" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="I50" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="I51" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="G52" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="I52" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="I53" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H54" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="I54" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="G55" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C13" s="3" t="s">
+      <c r="H55" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="I55" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J55" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="G56" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C14" s="3" t="s">
+      <c r="H56" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="I56" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="G57" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="F23" s="3" t="s">
+      <c r="H57" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="I57" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="G58" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H58" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="I58" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="G59" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H59" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="I59" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="G60" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H60" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="I60" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="G61" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="H61" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="I61" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J61" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H62" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="I62" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A63" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="B63" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="G23" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H26" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H28" s="4" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="G29" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H29" s="4" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="G30" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="G31" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="H31" s="4" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="H32" s="4" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="G33" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="H33" s="4" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="G34" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H34" s="4" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="G35" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="H35" s="4" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="G36" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="H36" s="4" t="s">
+      <c r="C63" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="G63" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H63" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="I63" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J63" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A64" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="G64" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H64" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="I64" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A65" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="G65" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H65" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="I65" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J65" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A66" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="G66" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H66" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="I66" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A67" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="G67" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H67" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="I67" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J67" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A68" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="G68" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H68" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="I68" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A69" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="B69" s="3" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="G37" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="H37" s="4" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="G38" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H38" s="4" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="G39" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H39" s="4" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="G40" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H40" s="4" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="G41" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H41" s="4" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="G42" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H42" s="4" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="G43" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H43" s="4" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="G44" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H44" s="4" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="G45" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H45" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="G46" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H46" s="4" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="G47" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H47" s="4" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="G48" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H48" s="4" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="G49" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H49" s="4" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="G50" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H50" s="4" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="G51" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H51" s="4" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="G52" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H52" s="4" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="G53" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H53" s="4" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="G54" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H54" s="4" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="D55" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="G55" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="H55" s="4" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="D56" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="G56" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="H56" s="4" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="D57" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="G57" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="H57" s="4" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="D58" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="G58" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="H58" s="4" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="D59" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="G59" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H59" s="4" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="D60" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="G60" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="H60" s="4" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="D61" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="G61" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="H61" s="4" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="D62" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="G62" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H62" s="4" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="D63" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="E63" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="G63" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H63" s="4" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="D64" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="E64" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="F64" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="G64" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H64" s="4" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="D65" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="E65" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="G65" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="H65" s="4" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="D66" s="4" t="s">
-        <v>350</v>
-      </c>
-      <c r="E66" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="G66" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="H66" s="4" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="D67" s="4" t="s">
-        <v>355</v>
-      </c>
-      <c r="E67" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="G67" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="H67" s="4" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="D68" s="4" t="s">
-        <v>361</v>
-      </c>
-      <c r="E68" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="G68" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="H68" s="4" t="s">
-        <v>364</v>
+      <c r="C69" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="G69" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H69" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="I69" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J69" s="3" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A70" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="G70" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H70" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="I70" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>393</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1"/>
+  <autoFilter ref="A1:J1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -3443,392 +4054,422 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>365</v>
+        <v>399</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>366</v>
+        <v>400</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>367</v>
+        <v>401</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>368</v>
+        <v>402</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>369</v>
+        <v>403</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>370</v>
+        <v>404</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>371</v>
+        <v>405</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>373</v>
+        <v>407</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>374</v>
+        <v>408</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>375</v>
+        <v>409</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>376</v>
+        <v>410</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>377</v>
+        <v>411</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>196</v>
+        <v>212</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>209</v>
+        <v>225</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>378</v>
+        <v>412</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>238</v>
+        <v>254</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>235</v>
+        <v>251</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>380</v>
+        <v>414</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>381</v>
+        <v>415</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>328</v>
+        <v>349</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>382</v>
+        <v>416</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>383</v>
+        <v>417</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>338</v>
+        <v>360</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>384</v>
+        <v>418</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>385</v>
+        <v>419</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>350</v>
+        <v>372</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>351</v>
+        <v>373</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>347</v>
+        <v>369</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>355</v>
+        <v>377</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>354</v>
+        <v>376</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>361</v>
+        <v>383</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>362</v>
+        <v>384</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>359</v>
+        <v>381</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>394</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:C1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="18" style="8" customWidth="1"/>
+    <col min="1" max="1" width="18" style="12" customWidth="1"/>
     <col min="2" max="2" width="90" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
-        <v>386</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>387</v>
+      <c r="A1" s="13" t="s">
+        <v>420</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
-        <v>388</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>389</v>
+      <c r="A2" s="13" t="s">
+        <v>422</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="10" t="s">
-        <v>390</v>
+      <c r="B3" s="14" t="s">
+        <v>424</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
-        <v>391</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>392</v>
+      <c r="A4" s="13" t="s">
+        <v>425</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="10" t="s">
-        <v>393</v>
+      <c r="B5" s="14" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>428</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/docs/frontend_기능명세서.xlsx
+++ b/docs/frontend_기능명세서.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="438">
   <si>
     <t>ID</t>
   </si>
@@ -444,6 +444,9 @@
     <t>GET /api/v1/users/me/scenarios, DELETE /api/v1/scenarios/:scenarioId</t>
   </si>
   <si>
+    <t>화면 구현, 브라우저 확인 전. 목록·편집·테스트 플레이·내보내기·삭제</t>
+  </si>
+  <si>
     <t>FE-EDT-02</t>
   </si>
   <si>
@@ -462,6 +465,9 @@
     <t>POST /api/v1/scenarios</t>
   </si>
   <si>
+    <t>화면 구현, 브라우저 확인 전. 플레이 가능한 템플릿(탑 시나리오)에서 시작</t>
+  </si>
+  <si>
     <t>FE-EDT-03</t>
   </si>
   <si>
@@ -477,6 +483,9 @@
     <t>POST /api/v1/scenarios/import</t>
   </si>
   <si>
+    <t>화면 구현, 브라우저 확인 전. .trpg/.zip 은 서버 가져오기, .yaml 은 편집기에서 열어 고친 뒤 저장</t>
+  </si>
+  <si>
     <t>FE-EDT-04</t>
   </si>
   <si>
@@ -489,6 +498,9 @@
     <t>GET /api/v1/scenarios/:scenarioId/export</t>
   </si>
   <si>
+    <t>화면 구현, 브라우저 확인 전</t>
+  </si>
+  <si>
     <t>FE-EDT-05</t>
   </si>
   <si>
@@ -507,6 +519,9 @@
     <t>GET /api/v1/scenarios/:scenarioId/source, GET /api/v1/scenarios/schema</t>
   </si>
   <si>
+    <t>화면 구현, 브라우저 확인 전. Monaco + monaco-yaml, 스키마 자동완성/툴팁, Ctrl+S 저장</t>
+  </si>
+  <si>
     <t>FE-EDT-06</t>
   </si>
   <si>
@@ -522,6 +537,9 @@
     <t>POST /api/v1/scenarios/validate</t>
   </si>
   <si>
+    <t>화면 구현, 브라우저 확인 전. 입력 0.6초 후 서버 검증, 편집기 줄 표시, 클릭 시 해당 줄로 이동</t>
+  </si>
+  <si>
     <t>FE-EDT-07</t>
   </si>
   <si>
@@ -534,6 +552,9 @@
     <t>PUT /api/v1/scenarios/:scenarioId</t>
   </si>
   <si>
+    <t>화면 구현, 브라우저 확인 전. 변경 메모, 미저장 이탈 경고(라우터·새로고침)</t>
+  </si>
+  <si>
     <t>FE-EDT-08</t>
   </si>
   <si>
@@ -549,6 +570,9 @@
     <t>PATCH /api/v1/scenarios/:scenarioId/visibility</t>
   </si>
   <si>
+    <t>화면 구현, 브라우저 확인 전. 링크 복사 없음</t>
+  </si>
+  <si>
     <t>FE-EDT-09</t>
   </si>
   <si>
@@ -564,6 +588,9 @@
     <t>장면/아이템/NPC/이벤트/엔딩 탭별 폼 편집, 코드 모드와 양방향 동기화</t>
   </si>
   <si>
+    <t>화면 구현, 브라우저 확인 전. 폼 대신 블록 코딩(Blockly). 블록/코드 탭 전환, YAML 양방향 변환(헤드리스 왕복 테스트 통과), 검증 오류 클릭 시 해당 블록 선택. 룰셋·프리셋·상태이상은 코드 탭</t>
+  </si>
+  <si>
     <t>FE-EDT-10</t>
   </si>
   <si>
@@ -615,7 +642,7 @@
     <t>POST /api/v1/scenarios/:scenarioId/test-sessions, PATCH /api/v1/sessions/:sessionId/debug/state</t>
   </si>
   <si>
-    <t>1인 플레이(/play) + 주사위 고정. 플래그/스탯 편집 패널 없음</t>
+    <t>화면 구현, 브라우저 확인 전. /play?scenario=&lt;id&gt; + 디버그 패널(주사위·플래그·변수·HP·순간이동·아이템)</t>
   </si>
   <si>
     <t>FE-EDT-13</t>
@@ -1325,7 +1352,7 @@
       <b/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1350,11 +1377,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0F0F0"/>
       </patternFill>
     </fill>
     <fill>
@@ -1400,7 +1422,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1429,10 +1451,7 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2012,7 +2031,7 @@
       <c r="H7" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="I7" s="9" t="s">
+      <c r="I7" s="8" t="s">
         <v>46</v>
       </c>
       <c r="J7" s="3" t="s">
@@ -2044,7 +2063,7 @@
       <c r="H8" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="I8" s="10" t="s">
+      <c r="I8" s="9" t="s">
         <v>55</v>
       </c>
       <c r="J8" s="3" t="s">
@@ -2076,7 +2095,7 @@
       <c r="H9" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="I9" s="9" t="s">
+      <c r="I9" s="8" t="s">
         <v>46</v>
       </c>
       <c r="J9" s="3" t="s">
@@ -2140,7 +2159,7 @@
       <c r="H11" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="I11" s="10" t="s">
+      <c r="I11" s="9" t="s">
         <v>55</v>
       </c>
       <c r="J11" s="3" t="s">
@@ -2268,7 +2287,7 @@
       <c r="H15" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="I15" s="10" t="s">
+      <c r="I15" s="9" t="s">
         <v>55</v>
       </c>
       <c r="J15" s="3" t="s">
@@ -2486,7 +2505,7 @@
       <c r="F22" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="G22" s="11" t="s">
+      <c r="G22" s="10" t="s">
         <v>134</v>
       </c>
       <c r="H22" s="4" t="s">
@@ -2525,82 +2544,82 @@
         <v>142</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>42</v>
+        <v>143</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>138</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G24" s="5" t="s">
         <v>15</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>42</v>
+        <v>150</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>138</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G25" s="5" t="s">
         <v>15</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>42</v>
+        <v>156</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>138</v>
@@ -2609,187 +2628,187 @@
         <v>139</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G26" s="5" t="s">
         <v>15</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>42</v>
+        <v>161</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>138</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="G27" s="5" t="s">
         <v>15</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>42</v>
+        <v>168</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>138</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="G28" s="5" t="s">
         <v>15</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>42</v>
+        <v>174</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>138</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="G29" s="5" t="s">
         <v>15</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>42</v>
+        <v>179</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>138</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="G30" s="5" t="s">
         <v>15</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>42</v>
+        <v>185</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>138</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="G31" s="7" t="s">
         <v>39</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>42</v>
+        <v>191</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>137</v>
@@ -2798,19 +2817,19 @@
         <v>138</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="G32" s="7" t="s">
         <v>39</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="I32" s="8" t="s">
         <v>41</v>
@@ -2821,28 +2840,28 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>138</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="G33" s="7" t="s">
         <v>39</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="I33" s="8" t="s">
         <v>41</v>
@@ -2853,60 +2872,60 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>138</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="G34" s="5" t="s">
         <v>15</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="I34" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="I34" s="8" t="s">
         <v>46</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>138</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="G35" s="7" t="s">
         <v>39</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="I35" s="8" t="s">
         <v>41</v>
@@ -2917,28 +2936,28 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>138</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="G36" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="G36" s="10" t="s">
         <v>134</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="I36" s="8" t="s">
         <v>41</v>
@@ -2949,28 +2968,28 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>138</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="G37" s="7" t="s">
         <v>39</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="I37" s="8" t="s">
         <v>41</v>
@@ -2981,30 +3000,30 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="G38" s="5" t="s">
         <v>15</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="I38" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="I38" s="9" t="s">
         <v>55</v>
       </c>
       <c r="J38" s="3" t="s">
@@ -3013,30 +3032,30 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="G39" s="5" t="s">
         <v>15</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="I39" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="I39" s="9" t="s">
         <v>55</v>
       </c>
       <c r="J39" s="3" t="s">
@@ -3045,30 +3064,30 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>85</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="G40" s="5" t="s">
         <v>15</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="I40" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="I40" s="9" t="s">
         <v>55</v>
       </c>
       <c r="J40" s="3" t="s">
@@ -3077,30 +3096,30 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="G41" s="5" t="s">
         <v>15</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="I41" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="I41" s="9" t="s">
         <v>55</v>
       </c>
       <c r="J41" s="3" t="s">
@@ -3109,30 +3128,30 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="G42" s="5" t="s">
         <v>15</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="I42" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="I42" s="9" t="s">
         <v>55</v>
       </c>
       <c r="J42" s="3" t="s">
@@ -3141,30 +3160,30 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="D43" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>237</v>
-      </c>
       <c r="E43" s="3" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="G43" s="5" t="s">
         <v>15</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="I43" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="I43" s="9" t="s">
         <v>55</v>
       </c>
       <c r="J43" s="3" t="s">
@@ -3173,30 +3192,30 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="G44" s="5" t="s">
         <v>15</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="I44" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="I44" s="9" t="s">
         <v>55</v>
       </c>
       <c r="J44" s="3" t="s">
@@ -3205,92 +3224,92 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="G45" s="5" t="s">
         <v>15</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="I45" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="I45" s="8" t="s">
         <v>46</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="G46" s="5" t="s">
         <v>15</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="I46" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="I46" s="8" t="s">
         <v>46</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="G47" s="5" t="s">
         <v>15</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="I47" s="8" t="s">
         <v>41</v>
@@ -3301,92 +3320,92 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="G48" s="5" t="s">
         <v>15</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="I48" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="I48" s="8" t="s">
         <v>46</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="G49" s="5" t="s">
         <v>15</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="I49" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="I49" s="8" t="s">
         <v>46</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="G50" s="5" t="s">
         <v>15</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="I50" s="8" t="s">
         <v>41</v>
@@ -3397,28 +3416,28 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="G51" s="5" t="s">
         <v>15</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="I51" s="8" t="s">
         <v>41</v>
@@ -3429,28 +3448,28 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="G52" s="5" t="s">
         <v>15</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="I52" s="8" t="s">
         <v>41</v>
@@ -3461,28 +3480,28 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="G53" s="5" t="s">
         <v>15</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="I53" s="8" t="s">
         <v>41</v>
@@ -3493,28 +3512,28 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="G54" s="5" t="s">
         <v>15</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="I54" s="8" t="s">
         <v>41</v>
@@ -3525,28 +3544,28 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="G55" s="7" t="s">
         <v>39</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="I55" s="8" t="s">
         <v>41</v>
@@ -3557,60 +3576,60 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="G56" s="7" t="s">
         <v>39</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="I56" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="I56" s="8" t="s">
         <v>46</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="G57" s="7" t="s">
         <v>39</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="I57" s="8" t="s">
         <v>41</v>
@@ -3621,28 +3640,28 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="G58" s="7" t="s">
         <v>39</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="I58" s="8" t="s">
         <v>41</v>
@@ -3653,28 +3672,28 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="G59" s="5" t="s">
         <v>15</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="I59" s="8" t="s">
         <v>41</v>
@@ -3685,28 +3704,28 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="G60" s="7" t="s">
         <v>39</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="I60" s="8" t="s">
         <v>41</v>
@@ -3717,28 +3736,28 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="G61" s="11" t="s">
+        <v>353</v>
+      </c>
+      <c r="G61" s="10" t="s">
         <v>134</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="I61" s="8" t="s">
         <v>41</v>
@@ -3749,60 +3768,60 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="G62" s="5" t="s">
         <v>15</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="I62" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="I62" s="8" t="s">
         <v>46</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>126</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="G63" s="5" t="s">
         <v>15</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="I63" s="8" t="s">
         <v>41</v>
@@ -3813,28 +3832,28 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="G64" s="5" t="s">
         <v>15</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="I64" s="8" t="s">
         <v>41</v>
@@ -3845,28 +3864,28 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="G65" s="7" t="s">
         <v>39</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="I65" s="8" t="s">
         <v>41</v>
@@ -3877,28 +3896,28 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="G66" s="7" t="s">
         <v>39</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="I66" s="8" t="s">
         <v>41</v>
@@ -3909,28 +3928,28 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="G67" s="7" t="s">
         <v>39</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="I67" s="8" t="s">
         <v>41</v>
@@ -3941,28 +3960,28 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="G68" s="7" t="s">
         <v>39</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="I68" s="8" t="s">
         <v>41</v>
@@ -3973,66 +3992,66 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="G69" s="7" t="s">
         <v>15</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="I69" s="6" t="s">
         <v>17</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="G70" s="7" t="s">
         <v>15</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="I70" s="6" t="s">
         <v>17</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
     </row>
   </sheetData>
@@ -4054,13 +4073,13 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>401</v>
+        <v>410</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -4123,10 +4142,10 @@
         <v>85</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>403</v>
+        <v>412</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -4167,10 +4186,10 @@
         <v>112</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -4178,230 +4197,230 @@
         <v>139</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>407</v>
+        <v>416</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>369</v>
+        <v>378</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
     </row>
   </sheetData>
@@ -4416,56 +4435,56 @@
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="18" style="12" customWidth="1"/>
+    <col min="1" max="1" width="18" style="11" customWidth="1"/>
     <col min="2" max="2" width="90" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
-        <v>420</v>
-      </c>
-      <c r="B1" s="14" t="s">
-        <v>421</v>
+      <c r="A1" s="12" t="s">
+        <v>429</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
-        <v>422</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>423</v>
+      <c r="A2" s="12" t="s">
+        <v>431</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="14" t="s">
-        <v>424</v>
+      <c r="B3" s="13" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
-        <v>425</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>426</v>
+      <c r="A4" s="12" t="s">
+        <v>434</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>435</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="14" t="s">
-        <v>427</v>
+      <c r="B5" s="13" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="14" t="s">
-        <v>428</v>
+      <c r="B6" s="13" t="s">
+        <v>437</v>
       </c>
     </row>
   </sheetData>
